--- a/Docs/XLXS/Notes1.xlsx
+++ b/Docs/XLXS/Notes1.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Project\me-api\Docs\XLXS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3485C19-E45C-42A3-B45B-D35D27D50001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E49B5F-8135-459B-825B-7F90F6399A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5EE9C587-9A37-4644-AEFC-39045B8C21B3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mongodb Atlas (Testing)" sheetId="1" r:id="rId1"/>
+    <sheet name="ME Configration" sheetId="1" r:id="rId1"/>
     <sheet name="Mangodb Atlas (Me)" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>Connection URL</t>
   </si>
@@ -97,13 +97,46 @@
   </si>
   <si>
     <t>DB connection URL</t>
+  </si>
+  <si>
+    <t>Resend Email Token</t>
+  </si>
+  <si>
+    <t>re_c1ifbhbW_3hmVkzKS7MZPWw6NRNhy1NaJ</t>
+  </si>
+  <si>
+    <t>Resend Email Account Password</t>
+  </si>
+  <si>
+    <t>Resend Email Account Email</t>
+  </si>
+  <si>
+    <t>Twilio Email Account Email</t>
+  </si>
+  <si>
+    <t>Twilio Email Account Password</t>
+  </si>
+  <si>
+    <t>ACf669c20bff5dd19e797ae06f734e18d2</t>
+  </si>
+  <si>
+    <t>0d4ef675d1a5b7b40bbdfc81d11515be</t>
+  </si>
+  <si>
+    <t>Twilio SID</t>
+  </si>
+  <si>
+    <t>Twilio Token</t>
+  </si>
+  <si>
+    <t>Twailo Phone number</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,13 +165,39 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -154,10 +213,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -493,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FBFBC33-9762-44AB-9022-6B789EE3328B}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.5703125" style="1" customWidth="1"/>
@@ -523,8 +586,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -560,83 +623,151 @@
         <v>16</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="B17" s="3">
+        <v>18142574429</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{CC895CAB-4A16-4A1F-A043-BADE70CB114E}"/>
+    <hyperlink ref="B11" r:id="rId2" xr:uid="{3B37AC6C-ED66-4D40-90C5-6AD6228501AD}"/>
+    <hyperlink ref="B12" r:id="rId3" xr:uid="{E5149E38-6CE4-417D-8790-FC1AB2012C6D}"/>
+    <hyperlink ref="B13" r:id="rId4" xr:uid="{667B803B-FE5F-4A57-9D07-3CDBA988083F}"/>
+    <hyperlink ref="B14" r:id="rId5" xr:uid="{8909FF31-F0D6-46A2-BDE2-9D9EAE80C5B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/XLXS/Notes1.xlsx
+++ b/Docs/XLXS/Notes1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Project\me-api\Docs\XLXS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E49B5F-8135-459B-825B-7F90F6399A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11348E50-40E2-4E22-8306-3B9D045D5E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5EE9C587-9A37-4644-AEFC-39045B8C21B3}"/>
   </bookViews>
